--- a/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.15465</v>
+        <v>0.28</v>
       </c>
       <c r="E2">
-        <v>0.2093</v>
+        <v>0.267</v>
       </c>
       <c r="F2">
-        <v>0.09480000000000001</v>
+        <v>0.0608</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>273.6</v>
+        <v>21.8</v>
       </c>
       <c r="L2">
-        <v>0.4022346368715084</v>
+        <v>0.2171314741035857</v>
       </c>
       <c r="M2">
-        <v>192.933</v>
+        <v>21.8</v>
       </c>
       <c r="N2">
-        <v>0.1186257993113625</v>
+        <v>0.1438943894389439</v>
       </c>
       <c r="O2">
-        <v>0.7051644736842104</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>192.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q2">
-        <v>0.1186055090998524</v>
+        <v>0.1438943894389439</v>
       </c>
       <c r="R2">
-        <v>0.7050438596491228</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>0.03299999999998704</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0001710438338697218</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1262.9</v>
+        <v>133.5</v>
       </c>
       <c r="V2">
-        <v>0.7765002459419577</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="W2">
-        <v>0.2737029068894782</v>
+        <v>0.1349009900990099</v>
       </c>
       <c r="X2">
-        <v>0.07281135577101264</v>
+        <v>0.1118987012866159</v>
       </c>
       <c r="Y2">
-        <v>0.2008915511184655</v>
+        <v>0.02300228881239397</v>
       </c>
       <c r="Z2">
-        <v>5.008836524300442</v>
+        <v>3.803030303030305</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07172280344748032</v>
+        <v>0.1090102985474391</v>
       </c>
       <c r="AC2">
-        <v>-0.07172280344748032</v>
+        <v>-0.1090102985474391</v>
       </c>
       <c r="AD2">
-        <v>34.1</v>
+        <v>15.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>34.1</v>
+        <v>15.2</v>
       </c>
       <c r="AG2">
-        <v>-1228.8</v>
+        <v>-118.3</v>
       </c>
       <c r="AH2">
-        <v>0.02053598313760915</v>
+        <v>0.09118176364727054</v>
       </c>
       <c r="AI2">
-        <v>0.02946768060836502</v>
+        <v>0.08573040045121263</v>
       </c>
       <c r="AJ2">
-        <v>-3.090543259557345</v>
+        <v>-3.563253012048192</v>
       </c>
       <c r="AK2">
-        <v>11.62535477767263</v>
+        <v>-2.700913242009133</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BSP Financial Group Limited (ASX:BFL)</t>
+          <t>Kina Securities Limited (ASX:KSL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0623</v>
+        <v>0.28</v>
       </c>
       <c r="E3">
-        <v>0.0906</v>
+        <v>0.267</v>
+      </c>
+      <c r="F3">
+        <v>0.0608</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,215 +734,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>249</v>
+        <v>21.8</v>
       </c>
       <c r="L3">
-        <v>0.4197572488199595</v>
+        <v>0.2171314741035857</v>
       </c>
       <c r="M3">
-        <v>174.133</v>
+        <v>21.8</v>
       </c>
       <c r="N3">
-        <v>0.1202575966850829</v>
+        <v>0.1438943894389439</v>
       </c>
       <c r="O3">
-        <v>0.6993293172690762</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>174.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q3">
-        <v>0.1202348066298343</v>
+        <v>0.1438943894389439</v>
       </c>
       <c r="R3">
-        <v>0.6991967871485943</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0.03299999999998704</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.0001895103168267189</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1139</v>
+        <v>133.5</v>
       </c>
       <c r="V3">
-        <v>0.7866022099447514</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="W3">
-        <v>0.286536248561565</v>
+        <v>0.1349009900990099</v>
       </c>
       <c r="X3">
-        <v>0.07141452628624258</v>
+        <v>0.1118987012866159</v>
       </c>
       <c r="Y3">
-        <v>0.2151217222753224</v>
+        <v>0.02300228881239397</v>
       </c>
       <c r="Z3">
-        <v>4.219061166429587</v>
+        <v>3.803030303030305</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07119525611509157</v>
+        <v>0.1090102985474391</v>
       </c>
       <c r="AC3">
-        <v>-0.07119525611509157</v>
+        <v>-0.1090102985474391</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>15.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19</v>
+        <v>15.2</v>
       </c>
       <c r="AG3">
-        <v>-1120</v>
+        <v>-118.3</v>
       </c>
       <c r="AH3">
-        <v>0.01295160190865712</v>
+        <v>0.09118176364727054</v>
       </c>
       <c r="AI3">
-        <v>0.01937786843447221</v>
+        <v>0.08573040045121263</v>
       </c>
       <c r="AJ3">
-        <v>-3.414634146341463</v>
+        <v>-3.563253012048192</v>
       </c>
       <c r="AK3">
-        <v>7.066246056782334</v>
+        <v>-2.700913242009133</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kina Securities Limited (ASX:KSL)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.247</v>
-      </c>
-      <c r="E4">
-        <v>0.328</v>
-      </c>
-      <c r="F4">
-        <v>0.09480000000000001</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>24.6</v>
-      </c>
-      <c r="L4">
-        <v>0.2827586206896552</v>
-      </c>
-      <c r="M4">
-        <v>18.8</v>
-      </c>
-      <c r="N4">
-        <v>0.1053811659192825</v>
-      </c>
-      <c r="O4">
-        <v>0.7642276422764227</v>
-      </c>
-      <c r="P4">
-        <v>18.8</v>
-      </c>
-      <c r="Q4">
-        <v>0.1053811659192825</v>
-      </c>
-      <c r="R4">
-        <v>0.7642276422764227</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>123.9</v>
-      </c>
-      <c r="V4">
-        <v>0.6945067264573991</v>
-      </c>
-      <c r="W4">
-        <v>0.2608695652173914</v>
-      </c>
-      <c r="X4">
-        <v>0.07420818525578271</v>
-      </c>
-      <c r="Y4">
-        <v>0.1866613799616086</v>
-      </c>
-      <c r="Z4">
-        <v>-18.12500000000001</v>
-      </c>
-      <c r="AA4">
-        <v>-0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07225035077986906</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07225035077986906</v>
-      </c>
-      <c r="AD4">
-        <v>15.1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>15.1</v>
-      </c>
-      <c r="AG4">
-        <v>-108.8</v>
-      </c>
-      <c r="AH4">
-        <v>0.07803617571059432</v>
-      </c>
-      <c r="AI4">
-        <v>0.08545557441992077</v>
-      </c>
-      <c r="AJ4">
-        <v>-1.563218390804598</v>
-      </c>
-      <c r="AK4">
-        <v>-2.060606060606061</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.28</v>
+        <v>0.223</v>
       </c>
       <c r="E2">
-        <v>0.267</v>
+        <v>0.236</v>
       </c>
       <c r="F2">
-        <v>0.0608</v>
+        <v>0.132</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>21.8</v>
+        <v>32.9</v>
       </c>
       <c r="L2">
-        <v>0.2171314741035857</v>
+        <v>0.3187984496124031</v>
       </c>
       <c r="M2">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="N2">
-        <v>0.1438943894389439</v>
+        <v>0.135755258126195</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>0.6474164133738602</v>
       </c>
       <c r="P2">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q2">
-        <v>0.1438943894389439</v>
+        <v>0.135755258126195</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0.6474164133738602</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>133.5</v>
+        <v>159.4</v>
       </c>
       <c r="V2">
-        <v>0.8811881188118812</v>
+        <v>1.015933715742511</v>
       </c>
       <c r="W2">
-        <v>0.1349009900990099</v>
+        <v>0.202961135101789</v>
       </c>
       <c r="X2">
-        <v>0.1118987012866159</v>
+        <v>0.09141626022377748</v>
       </c>
       <c r="Y2">
-        <v>0.02300228881239397</v>
+        <v>0.1115448748780115</v>
       </c>
       <c r="Z2">
-        <v>3.803030303030305</v>
+        <v>5.931034482758626</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1090102985474391</v>
+        <v>0.09006319196219201</v>
       </c>
       <c r="AC2">
-        <v>-0.1090102985474391</v>
+        <v>-0.09006319196219201</v>
       </c>
       <c r="AD2">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="AG2">
-        <v>-118.3</v>
+        <v>-146.6</v>
       </c>
       <c r="AH2">
-        <v>0.09118176364727054</v>
+        <v>0.07542722451384797</v>
       </c>
       <c r="AI2">
-        <v>0.08573040045121263</v>
+        <v>0.06956521739130435</v>
       </c>
       <c r="AJ2">
-        <v>-3.563253012048192</v>
+        <v>-14.23300970873785</v>
       </c>
       <c r="AK2">
-        <v>-2.700913242009133</v>
+        <v>-5.959349593495936</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.28</v>
+        <v>0.223</v>
       </c>
       <c r="E3">
-        <v>0.267</v>
+        <v>0.236</v>
       </c>
       <c r="F3">
-        <v>0.0608</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>21.8</v>
+        <v>32.9</v>
       </c>
       <c r="L3">
-        <v>0.2171314741035857</v>
+        <v>0.3187984496124031</v>
       </c>
       <c r="M3">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="N3">
-        <v>0.1438943894389439</v>
+        <v>0.135755258126195</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0.6474164133738602</v>
       </c>
       <c r="P3">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q3">
-        <v>0.1438943894389439</v>
+        <v>0.135755258126195</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0.6474164133738602</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>133.5</v>
+        <v>159.4</v>
       </c>
       <c r="V3">
-        <v>0.8811881188118812</v>
+        <v>1.015933715742511</v>
       </c>
       <c r="W3">
-        <v>0.1349009900990099</v>
+        <v>0.202961135101789</v>
       </c>
       <c r="X3">
-        <v>0.1118987012866159</v>
+        <v>0.09141626022377748</v>
       </c>
       <c r="Y3">
-        <v>0.02300228881239397</v>
+        <v>0.1115448748780115</v>
       </c>
       <c r="Z3">
-        <v>3.803030303030305</v>
+        <v>5.931034482758626</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1090102985474391</v>
+        <v>0.09006319196219201</v>
       </c>
       <c r="AC3">
-        <v>-0.1090102985474391</v>
+        <v>-0.09006319196219201</v>
       </c>
       <c r="AD3">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="AG3">
-        <v>-118.3</v>
+        <v>-146.6</v>
       </c>
       <c r="AH3">
-        <v>0.09118176364727054</v>
+        <v>0.07542722451384797</v>
       </c>
       <c r="AI3">
-        <v>0.08573040045121263</v>
+        <v>0.06956521739130435</v>
       </c>
       <c r="AJ3">
-        <v>-3.563253012048192</v>
+        <v>-14.23300970873785</v>
       </c>
       <c r="AK3">
-        <v>-2.700913242009133</v>
+        <v>-5.959349593495936</v>
       </c>
       <c r="AL3">
         <v>0</v>
